--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_10_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_10_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,82 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
     <t>qd_tot</t>
   </si>
   <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
     <t>Ibr_from_i_tot</t>
   </si>
   <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
+    <t>slack_tot</t>
   </si>
   <si>
     <t>qinj_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>nn_input</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
   </si>
   <si>
     <t>Iinj_r_tot</t>
   </si>
   <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>nn_input</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>1.28 (2.18)</t>
-  </si>
-  <si>
-    <t>68846.00 (71109.52 &gt; 3.18%)</t>
-  </si>
-  <si>
-    <t>1.34 (2.18)</t>
-  </si>
-  <si>
-    <t>68877.38 (71109.52 &gt; 3.13%)</t>
-  </si>
-  <si>
-    <t>-0.84 (2.18)</t>
-  </si>
-  <si>
-    <t>70789.79 (71109.52 &gt; 1.09%)</t>
-  </si>
-  <si>
-    <t>-0.81 (2.18)</t>
-  </si>
-  <si>
-    <t>70357.27 (71109.52 &gt; 1.19%)</t>
+    <t>68883.90 (71109.52 &gt; 3.13%)</t>
+  </si>
+  <si>
+    <t>1.32 (218.10)</t>
+  </si>
+  <si>
+    <t>68900.38 (71109.52 &gt; 3.11%)</t>
+  </si>
+  <si>
+    <t>1.35 (218.10)</t>
+  </si>
+  <si>
+    <t>70789.77 (71109.52 &gt; 0.45%)</t>
+  </si>
+  <si>
+    <t>-0.84 (218.10)</t>
+  </si>
+  <si>
+    <t>70357.23 (71109.52 &gt; 1.06%)</t>
+  </si>
+  <si>
+    <t>-0.81 (218.10)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -489,33 +492,33 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1.050897070451705</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1.05093338982542</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.1115594878792763</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.1229525282979012</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>1.050836099771223</v>
-      </c>
-      <c r="C3">
-        <v>1.050926140198884</v>
-      </c>
-      <c r="D3">
-        <v>0.1115514561533928</v>
-      </c>
-      <c r="E3">
-        <v>0.1229433864355087</v>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -523,16 +526,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.6683475375175476</v>
+        <v>2.844707552140716</v>
       </c>
       <c r="C4">
-        <v>0.6683641076087952</v>
+        <v>2.844764535324272</v>
       </c>
       <c r="D4">
-        <v>0.0002679010794963688</v>
+        <v>0.03320124372839928</v>
       </c>
       <c r="E4">
-        <v>0.0005598017596639693</v>
+        <v>0.02909409627318382</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -540,16 +543,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1.013028826375241</v>
+        <v>0.002371247857809067</v>
       </c>
       <c r="C5">
-        <v>1.013112317796136</v>
+        <v>0.002371261361986399</v>
       </c>
       <c r="D5">
-        <v>0.03502869978547096</v>
+        <v>3.64272236765828E-05</v>
       </c>
       <c r="E5">
-        <v>0.03845903277397156</v>
+        <v>0.0003170787822455168</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,16 +560,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>3.05282267613934</v>
+        <v>3.052896383561031</v>
       </c>
       <c r="C6">
-        <v>3.052959349703767</v>
+        <v>3.052959253669367</v>
       </c>
       <c r="D6">
-        <v>0.035128403455019</v>
+        <v>0.03512811660766602</v>
       </c>
       <c r="E6">
-        <v>0.03093836270272732</v>
+        <v>0.0309380330145359</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -574,16 +577,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.002371246227994561</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.002371272770687938</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>3.642739829956554E-05</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.0003170791314914823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -591,16 +594,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1.181674957275391</v>
+        <v>0.6683531403541565</v>
       </c>
       <c r="C8">
-        <v>1.181803822517395</v>
+        <v>0.6683645248413086</v>
       </c>
       <c r="D8">
-        <v>0.1123401969671249</v>
+        <v>0.0002679004392120987</v>
       </c>
       <c r="E8">
-        <v>0.1220208629965782</v>
+        <v>0.0005598025745712221</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -608,16 +611,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.0003578867952913541</v>
+        <v>0.0003137768339895176</v>
       </c>
       <c r="C9">
-        <v>0.0004266645315175057</v>
+        <v>0.0004093685876177727</v>
       </c>
       <c r="D9">
-        <v>0.1163971126079559</v>
+        <v>0.1163966357707977</v>
       </c>
       <c r="E9">
-        <v>0.1055909991264343</v>
+        <v>0.1055903881788254</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -625,16 +628,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>9.900526762853698</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>9.901150046155195</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.113837443292141</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.1044792979955673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -642,33 +645,33 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.063686110394244</v>
+        <v>1.013104802894383</v>
       </c>
       <c r="C11">
-        <v>1.063773933363631</v>
+        <v>1.013128196781221</v>
       </c>
       <c r="D11">
-        <v>0.03349814563989639</v>
+        <v>0.03503313660621643</v>
       </c>
       <c r="E11">
-        <v>0.03679946437478065</v>
+        <v>0.03846371546387672</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -676,16 +679,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>9.40562915802002</v>
+        <v>1.181767225265503</v>
       </c>
       <c r="C13">
-        <v>9.406185150146484</v>
+        <v>1.181812167167664</v>
       </c>
       <c r="D13">
-        <v>0.1159481257200241</v>
+        <v>0.1123480722308159</v>
       </c>
       <c r="E13">
-        <v>0.1088426858186722</v>
+        <v>0.1220298260450363</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -693,16 +696,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.5847111344337463</v>
+        <v>9.405957221984863</v>
       </c>
       <c r="C14">
-        <v>0.5847615003585815</v>
+        <v>9.406225204467773</v>
       </c>
       <c r="D14">
-        <v>3.417619882384315E-05</v>
+        <v>0.1159478649497032</v>
       </c>
       <c r="E14">
-        <v>0.0002998677373398095</v>
+        <v>0.1088423877954483</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,16 +713,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>2.84462627488461</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>2.844753416426961</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0.03320164233446121</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.02909445762634277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -727,67 +730,72 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.1252297163009644</v>
+        <v>0.1252355426549911</v>
       </c>
       <c r="C16">
-        <v>0.1252297163009644</v>
+        <v>0.1252355426549911</v>
       </c>
       <c r="D16">
-        <v>0.08213358372449875</v>
+        <v>0.08214931190013885</v>
       </c>
       <c r="E16">
-        <v>0.1084381267428398</v>
+        <v>0.1084563583135605</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" t="s">
-        <v>29</v>
+      <c r="B17">
+        <v>1.063756102569528</v>
+      </c>
+      <c r="C17">
+        <v>1.063780036562839</v>
+      </c>
+      <c r="D17">
+        <v>0.03350325673818588</v>
+      </c>
+      <c r="E17">
+        <v>0.03680471703410149</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
+      <c r="B19">
+        <v>0.5847507119178772</v>
+      </c>
+      <c r="C19">
+        <v>0.5847682356834412</v>
+      </c>
+      <c r="D19">
+        <v>3.417638072278351E-05</v>
+      </c>
+      <c r="E19">
+        <v>0.0002998676791321486</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>9.900904475545046</v>
+      </c>
+      <c r="C20">
+        <v>9.901195737041185</v>
+      </c>
+      <c r="D20">
+        <v>0.1138367876410484</v>
+      </c>
+      <c r="E20">
+        <v>0.1044786497950554</v>
       </c>
     </row>
   </sheetData>
